--- a/Reagent Usage dan Stock Reagent.xlsx
+++ b/Reagent Usage dan Stock Reagent.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramda\Documents\Zeta_Edit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F60032A-4B84-4699-8631-CBAB5797089E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AF07B3-0C8B-46E0-8059-E9A79EC6108B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44BE0AC2-6033-44C2-8356-2F41A96EBF2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Stock Barang" sheetId="1" r:id="rId1"/>
     <sheet name="Barang Masuk" sheetId="2" r:id="rId2"/>
-    <sheet name="Barang Keluar " sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Barang Keluar " sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="34">
   <si>
     <t>No</t>
   </si>
@@ -388,36 +388,6 @@
   </cellStyles>
   <dxfs count="15">
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -602,6 +572,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -624,13 +601,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -667,6 +637,36 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -687,22 +687,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1AC36863-5F67-4496-A2C7-808F86C284A1}" name="Table1" displayName="Table1" ref="B3:H21" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1AC36863-5F67-4496-A2C7-808F86C284A1}" name="Table1" displayName="Table1" ref="B3:H21" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
   <autoFilter ref="B3:H21" xr:uid="{1AC36863-5F67-4496-A2C7-808F86C284A1}"/>
   <tableColumns count="7">
-    <tableColumn id="2" xr3:uid="{E78837C8-954C-440F-BCB4-114AA4EBC159}" name="Kode Barang" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{BB8DB245-EB50-4D84-9B3E-D2CF46896708}" name="Nama Barang" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{36BAEBBD-D2E7-42F0-B8AF-873903FEFEA9}" name="Stok Awal " dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{3DA331B5-0C1B-4517-AC2B-660041411D0B}" name="Barang Masuk" dataDxfId="6">
+    <tableColumn id="2" xr3:uid="{E78837C8-954C-440F-BCB4-114AA4EBC159}" name="Kode Barang" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{BB8DB245-EB50-4D84-9B3E-D2CF46896708}" name="Nama Barang" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{36BAEBBD-D2E7-42F0-B8AF-873903FEFEA9}" name="Stok Awal " dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{3DA331B5-0C1B-4517-AC2B-660041411D0B}" name="Barang Masuk" dataDxfId="3">
       <calculatedColumnFormula>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4231B6CF-326F-44B2-8A60-3DCCDB55861D}" name="Barang Keluar " dataDxfId="5">
+    <tableColumn id="6" xr3:uid="{4231B6CF-326F-44B2-8A60-3DCCDB55861D}" name="Barang Keluar " dataDxfId="2">
       <calculatedColumnFormula>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{9472852C-4AF5-44FD-A6F5-E9EDEDD511AE}" name="Stock Akhir" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{9472852C-4AF5-44FD-A6F5-E9EDEDD511AE}" name="Stock Akhir" dataDxfId="1">
       <calculatedColumnFormula>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{C780F2FB-0F97-426F-AC7D-196550D5A9CF}" name="Satuan" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{C780F2FB-0F97-426F-AC7D-196550D5A9CF}" name="Satuan" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="F5" s="2">
         <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G5" s="13">
         <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>33</v>
@@ -1152,7 +1152,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="2">
-        <v>5900</v>
+        <v>5750</v>
       </c>
       <c r="E6" s="2">
         <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
@@ -1160,11 +1160,11 @@
       </c>
       <c r="F6" s="2">
         <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>1500</v>
+        <v>2375</v>
       </c>
       <c r="G6" s="13">
         <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>4400</v>
+        <v>3375</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>33</v>
@@ -1182,15 +1182,15 @@
       </c>
       <c r="E7" s="2">
         <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F7" s="2">
         <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>2250</v>
+        <v>3500</v>
       </c>
       <c r="G7" s="13">
         <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>5250</v>
+        <v>9000</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>33</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="F12" s="2">
         <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G12" s="14">
         <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>6375</v>
+        <v>6325</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>33</v>
@@ -1493,15 +1493,15 @@
     <mergeCell ref="B1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="greaterThan">
       <formula>3999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G10">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="greaterThan">
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="lessThan">
       <formula>500</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1545,13 +1545,19 @@
       <c r="B5" s="8">
         <v>1</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="7"/>
+      <c r="C5" s="9">
+        <v>46277</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E5" s="7" t="str">
         <f>IFERROR(VLOOKUP(D5,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F5" s="7"/>
+        <v>Kapur</v>
+      </c>
+      <c r="F5" s="7">
+        <v>5000</v>
+      </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="8">
@@ -4610,6 +4616,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{684DB87B-F02C-41BA-A196-5B8F96176BFB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C4F271-B1B8-49EF-AE8E-5ADDB846D57A}">
   <dimension ref="B4:K315"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4925,7 +4940,7 @@
         <v>Kapur</v>
       </c>
       <c r="F17" s="7">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="G17" t="s">
         <v>25</v>
@@ -4998,13 +5013,19 @@
       <c r="B21" s="8">
         <v>17</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
+      <c r="C21" s="9">
+        <v>46276</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="E21" s="7" t="str">
         <f>IFERROR(VLOOKUP(D21,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="7"/>
+        <v>Sandios</v>
+      </c>
+      <c r="F21" s="7">
+        <v>375</v>
+      </c>
       <c r="G21" t="s">
         <v>25</v>
       </c>
@@ -5013,13 +5034,19 @@
       <c r="B22" s="8">
         <v>18</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="C22" s="9">
+        <v>46277</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="E22" s="7" t="str">
         <f>IFERROR(VLOOKUP(D22,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="7"/>
+        <v>Sandios</v>
+      </c>
+      <c r="F22" s="7">
+        <v>125</v>
+      </c>
       <c r="G22" t="s">
         <v>25</v>
       </c>
@@ -5028,13 +5055,19 @@
       <c r="B23" s="8">
         <v>19</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
+      <c r="C23" s="9">
+        <v>46278</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="E23" s="7" t="str">
         <f>IFERROR(VLOOKUP(D23,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="7"/>
+        <v>Sandios</v>
+      </c>
+      <c r="F23" s="7">
+        <v>375</v>
+      </c>
       <c r="G23" t="s">
         <v>25</v>
       </c>
@@ -5043,13 +5076,19 @@
       <c r="B24" s="8">
         <v>20</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
+      <c r="C24" s="9">
+        <v>46277</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="E24" s="7" t="str">
         <f>IFERROR(VLOOKUP(D24,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="7"/>
+        <v>Carbon</v>
+      </c>
+      <c r="F24" s="7">
+        <v>500</v>
+      </c>
       <c r="G24" t="s">
         <v>25</v>
       </c>
@@ -5058,13 +5097,19 @@
       <c r="B25" s="8">
         <v>21</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
+      <c r="C25" s="9">
+        <v>46276</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="E25" s="7" t="str">
         <f>IFERROR(VLOOKUP(D25,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="7"/>
+        <v>Floculant</v>
+      </c>
+      <c r="F25" s="7">
+        <v>50</v>
+      </c>
       <c r="G25" t="s">
         <v>25</v>
       </c>
@@ -5073,13 +5118,19 @@
       <c r="B26" s="8">
         <v>22</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="C26" s="9">
+        <v>46267</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E26" s="7" t="str">
         <f>IFERROR(VLOOKUP(D26,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="7"/>
+        <v>Kapur</v>
+      </c>
+      <c r="F26" s="7">
+        <v>500</v>
+      </c>
       <c r="G26" t="s">
         <v>25</v>
       </c>
@@ -5088,13 +5139,19 @@
       <c r="B27" s="8">
         <v>23</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
+      <c r="C27" s="9">
+        <v>46268</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E27" s="7" t="str">
         <f>IFERROR(VLOOKUP(D27,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="7"/>
+        <v>Kapur</v>
+      </c>
+      <c r="F27" s="7">
+        <v>250</v>
+      </c>
       <c r="G27" t="s">
         <v>25</v>
       </c>
@@ -7738,13 +7795,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{684DB87B-F02C-41BA-A196-5B8F96176BFB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Reagent Usage dan Stock Reagent.xlsx
+++ b/Reagent Usage dan Stock Reagent.xlsx
@@ -388,6 +388,36 @@
   </cellStyles>
   <dxfs count="15">
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -572,13 +602,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -601,6 +624,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -637,36 +667,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -687,22 +687,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1AC36863-5F67-4496-A2C7-808F86C284A1}" name="Table1" displayName="Table1" ref="B3:H21" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1AC36863-5F67-4496-A2C7-808F86C284A1}" name="Table1" displayName="Table1" ref="B3:H21" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="B3:H21" xr:uid="{1AC36863-5F67-4496-A2C7-808F86C284A1}"/>
   <tableColumns count="7">
-    <tableColumn id="2" xr3:uid="{E78837C8-954C-440F-BCB4-114AA4EBC159}" name="Kode Barang" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{BB8DB245-EB50-4D84-9B3E-D2CF46896708}" name="Nama Barang" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{36BAEBBD-D2E7-42F0-B8AF-873903FEFEA9}" name="Stok Awal " dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{3DA331B5-0C1B-4517-AC2B-660041411D0B}" name="Barang Masuk" dataDxfId="3">
+    <tableColumn id="2" xr3:uid="{E78837C8-954C-440F-BCB4-114AA4EBC159}" name="Kode Barang" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{BB8DB245-EB50-4D84-9B3E-D2CF46896708}" name="Nama Barang" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{36BAEBBD-D2E7-42F0-B8AF-873903FEFEA9}" name="Stok Awal " dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{3DA331B5-0C1B-4517-AC2B-660041411D0B}" name="Barang Masuk" dataDxfId="6">
       <calculatedColumnFormula>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4231B6CF-326F-44B2-8A60-3DCCDB55861D}" name="Barang Keluar " dataDxfId="2">
+    <tableColumn id="6" xr3:uid="{4231B6CF-326F-44B2-8A60-3DCCDB55861D}" name="Barang Keluar " dataDxfId="5">
       <calculatedColumnFormula>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{9472852C-4AF5-44FD-A6F5-E9EDEDD511AE}" name="Stock Akhir" dataDxfId="1">
+    <tableColumn id="7" xr3:uid="{9472852C-4AF5-44FD-A6F5-E9EDEDD511AE}" name="Stock Akhir" dataDxfId="4">
       <calculatedColumnFormula>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{C780F2FB-0F97-426F-AC7D-196550D5A9CF}" name="Satuan" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{C780F2FB-0F97-426F-AC7D-196550D5A9CF}" name="Satuan" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1493,15 +1493,15 @@
     <mergeCell ref="B1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>3999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G10">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>500</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Reagent Usage dan Stock Reagent.xlsx
+++ b/Reagent Usage dan Stock Reagent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramda\Documents\Zeta_Edit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AF07B3-0C8B-46E0-8059-E9A79EC6108B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702BA5E7-3C29-4EE4-A6C3-5D30D134DF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44BE0AC2-6033-44C2-8356-2F41A96EBF2E}"/>
   </bookViews>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="34">
   <si>
     <t>No</t>
   </si>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="F12" s="2">
         <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="G12" s="14">
         <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>6325</v>
+        <v>6300</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>33</v>
@@ -5160,13 +5160,19 @@
       <c r="B28" s="8">
         <v>24</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
+      <c r="C28" s="9">
+        <v>46269</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="E28" s="7" t="str">
         <f>IFERROR(VLOOKUP(D28,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="7"/>
+        <v>Floculant</v>
+      </c>
+      <c r="F28" s="7">
+        <v>25</v>
+      </c>
       <c r="G28" t="s">
         <v>25</v>
       </c>

--- a/Reagent Usage dan Stock Reagent.xlsx
+++ b/Reagent Usage dan Stock Reagent.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramda\Documents\Zeta_Edit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702BA5E7-3C29-4EE4-A6C3-5D30D134DF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC2ADA7-55B6-4A5C-80AD-B0C43FB76B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44BE0AC2-6033-44C2-8356-2F41A96EBF2E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{44BE0AC2-6033-44C2-8356-2F41A96EBF2E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Stock Barang" sheetId="1" r:id="rId1"/>
-    <sheet name="Barang Masuk" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Barang Masuk" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
+    <sheet name="Stock Barang" sheetId="1" r:id="rId3"/>
     <sheet name="Barang Keluar " sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="34">
   <si>
     <t>No</t>
   </si>
@@ -388,6 +388,32 @@
   </cellStyles>
   <dxfs count="15">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -464,32 +490,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -696,13 +696,13 @@
     <tableColumn id="5" xr3:uid="{3DA331B5-0C1B-4517-AC2B-660041411D0B}" name="Barang Masuk" dataDxfId="6">
       <calculatedColumnFormula>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4231B6CF-326F-44B2-8A60-3DCCDB55861D}" name="Barang Keluar " dataDxfId="5">
-      <calculatedColumnFormula>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{4231B6CF-326F-44B2-8A60-3DCCDB55861D}" name="Barang Keluar " dataDxfId="0">
+      <calculatedColumnFormula>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{9472852C-4AF5-44FD-A6F5-E9EDEDD511AE}" name="Stock Akhir" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{9472852C-4AF5-44FD-A6F5-E9EDEDD511AE}" name="Stock Akhir" dataDxfId="5">
       <calculatedColumnFormula>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{C780F2FB-0F97-426F-AC7D-196550D5A9CF}" name="Satuan" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{C780F2FB-0F97-426F-AC7D-196550D5A9CF}" name="Satuan" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1044,476 +1044,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CAC8830-268B-489B-9A12-01936A5CA5A2}">
-  <dimension ref="B1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" style="10" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="B1" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2">
-        <v>150</v>
-      </c>
-      <c r="E4" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>150</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2">
-        <v>5000</v>
-      </c>
-      <c r="E5" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>3000</v>
-      </c>
-      <c r="G5" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>2000</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2">
-        <v>5750</v>
-      </c>
-      <c r="E6" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>2375</v>
-      </c>
-      <c r="G6" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>3375</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2">
-        <v>7500</v>
-      </c>
-      <c r="E7" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>5000</v>
-      </c>
-      <c r="F7" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>3500</v>
-      </c>
-      <c r="G7" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>9000</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="2">
-        <v>400</v>
-      </c>
-      <c r="E8" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>400</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="2">
-        <v>125</v>
-      </c>
-      <c r="E10" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>125</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="2">
-        <v>14975</v>
-      </c>
-      <c r="E11" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>14975</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="2">
-        <v>6425</v>
-      </c>
-      <c r="E12" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>125</v>
-      </c>
-      <c r="G12" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>6300</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="12"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="12"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="12"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="12"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="12"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="12"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="12"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="15">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="12"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:G1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
-      <formula>3999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G10">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>500</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>500</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E498DA0C-37B1-4354-B038-CA23BB50DFD0}">
   <dimension ref="B4:F334"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4615,12 +4145,482 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{684DB87B-F02C-41BA-A196-5B8F96176BFB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CAC8830-268B-489B-9A12-01936A5CA5A2}">
+  <dimension ref="B1:H21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="B1" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2">
+        <v>150</v>
+      </c>
+      <c r="E4" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>150</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E5" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>3000</v>
+      </c>
+      <c r="G5" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>2000</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5750</v>
+      </c>
+      <c r="E6" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>3725</v>
+      </c>
+      <c r="G6" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>2025</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2">
+        <v>7500</v>
+      </c>
+      <c r="E7" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>5000</v>
+      </c>
+      <c r="F7" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>3000</v>
+      </c>
+      <c r="G7" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>9500</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2">
+        <v>400</v>
+      </c>
+      <c r="E8" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>400</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="2">
+        <v>125</v>
+      </c>
+      <c r="E10" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>125</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2">
+        <v>14975</v>
+      </c>
+      <c r="E11" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>14975</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2">
+        <v>6425</v>
+      </c>
+      <c r="E12" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>6225</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="12"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="15">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+      <formula>3999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G10">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+      <formula>500</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+      <formula>500</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -4717,14 +4717,14 @@
         <v>46266</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E7" s="7" t="str">
         <f>IFERROR(VLOOKUP(D7,Table1[#All],2,0),"")</f>
-        <v>Carbon</v>
+        <v>Floculant</v>
       </c>
       <c r="F7" s="7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
@@ -4741,14 +4741,14 @@
         <v>46266</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E8" s="7" t="str">
         <f>IFERROR(VLOOKUP(D8,Table1[#All],2,0),"")</f>
-        <v>Kapur</v>
+        <v>Carbon</v>
       </c>
       <c r="F8" s="7">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="G8" t="s">
         <v>25</v>
@@ -4765,14 +4765,14 @@
         <v>46266</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E9" s="7" t="str">
         <f>IFERROR(VLOOKUP(D9,Table1[#All],2,0),"")</f>
-        <v>Floculant</v>
+        <v>Kapur</v>
       </c>
       <c r="F9" s="7">
-        <v>25</v>
+        <v>1250</v>
       </c>
       <c r="G9" t="s">
         <v>25</v>
@@ -4786,14 +4786,14 @@
         <v>46267</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" s="7" t="str">
         <f>IFERROR(VLOOKUP(D10,Table1[#All],2,0),"")</f>
-        <v>Carbon</v>
+        <v>Kapur</v>
       </c>
       <c r="F10" s="7">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G10" t="s">
         <v>25</v>
@@ -4814,7 +4814,7 @@
         <v>Sandios</v>
       </c>
       <c r="F11" s="7">
-        <v>275</v>
+        <v>375</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>
@@ -4825,17 +4825,17 @@
         <v>8</v>
       </c>
       <c r="C12" s="9">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E12" s="7" t="str">
         <f>IFERROR(VLOOKUP(D12,Table1[#All],2,0),"")</f>
-        <v>Sandios</v>
+        <v>Floculant</v>
       </c>
       <c r="F12" s="7">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s">
         <v>25</v>
@@ -4846,17 +4846,17 @@
         <v>9</v>
       </c>
       <c r="C13" s="9">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E13" s="7" t="str">
         <f>IFERROR(VLOOKUP(D13,Table1[#All],2,0),"")</f>
-        <v>Floculant</v>
+        <v>Carbon</v>
       </c>
       <c r="F13" s="7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="G13" t="s">
         <v>25</v>
@@ -4867,17 +4867,17 @@
         <v>10</v>
       </c>
       <c r="C14" s="9">
-        <v>46271</v>
+        <v>46268</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="7" t="str">
         <f>IFERROR(VLOOKUP(D14,Table1[#All],2,0),"")</f>
-        <v>Sandios</v>
+        <v>Kapur</v>
       </c>
       <c r="F14" s="7">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="G14" t="s">
         <v>25</v>
@@ -4888,17 +4888,17 @@
         <v>11</v>
       </c>
       <c r="C15" s="9">
-        <v>46271</v>
+        <v>46269</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="7" t="str">
         <f>IFERROR(VLOOKUP(D15,Table1[#All],2,0),"")</f>
-        <v>Kapur</v>
+        <v>Sandios</v>
       </c>
       <c r="F15" s="7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="G15" t="s">
         <v>25</v>
@@ -4909,17 +4909,17 @@
         <v>12</v>
       </c>
       <c r="C16" s="9">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E16" s="7" t="str">
         <f>IFERROR(VLOOKUP(D16,Table1[#All],2,0),"")</f>
-        <v>Sandios</v>
+        <v>Floculant</v>
       </c>
       <c r="F16" s="7">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
         <v>25</v>
@@ -4930,7 +4930,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="9">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>9</v>
@@ -4940,7 +4940,7 @@
         <v>Kapur</v>
       </c>
       <c r="F17" s="7">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="G17" t="s">
         <v>25</v>
@@ -4951,17 +4951,17 @@
         <v>14</v>
       </c>
       <c r="C18" s="9">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="7" t="str">
         <f>IFERROR(VLOOKUP(D18,Table1[#All],2,0),"")</f>
-        <v>Sandios</v>
+        <v>Kapur</v>
       </c>
       <c r="F18" s="7">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G18" t="s">
         <v>25</v>
@@ -4972,7 +4972,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="9">
-        <v>46274</v>
+        <v>46272</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>8</v>
@@ -4982,7 +4982,7 @@
         <v>Sandios</v>
       </c>
       <c r="F19" s="7">
-        <v>75</v>
+        <v>375</v>
       </c>
       <c r="G19" t="s">
         <v>25</v>
@@ -4993,17 +4993,17 @@
         <v>16</v>
       </c>
       <c r="C20" s="9">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" s="7" t="str">
         <f>IFERROR(VLOOKUP(D20,Table1[#All],2,0),"")</f>
-        <v>Carbon</v>
+        <v>Sandios</v>
       </c>
       <c r="F20" s="7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="G20" t="s">
         <v>25</v>
@@ -5014,17 +5014,17 @@
         <v>17</v>
       </c>
       <c r="C21" s="9">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" s="7" t="str">
         <f>IFERROR(VLOOKUP(D21,Table1[#All],2,0),"")</f>
-        <v>Sandios</v>
+        <v>Carbon</v>
       </c>
       <c r="F21" s="7">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="G21" t="s">
         <v>25</v>
@@ -5035,7 +5035,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="9">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>8</v>
@@ -5045,7 +5045,7 @@
         <v>Sandios</v>
       </c>
       <c r="F22" s="7">
-        <v>125</v>
+        <v>375</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
@@ -5056,17 +5056,17 @@
         <v>19</v>
       </c>
       <c r="C23" s="9">
-        <v>46278</v>
+        <v>46276</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E23" s="7" t="str">
         <f>IFERROR(VLOOKUP(D23,Table1[#All],2,0),"")</f>
-        <v>Sandios</v>
+        <v>Floculant</v>
       </c>
       <c r="F23" s="7">
-        <v>375</v>
+        <v>50</v>
       </c>
       <c r="G23" t="s">
         <v>25</v>
@@ -5077,7 +5077,7 @@
         <v>20</v>
       </c>
       <c r="C24" s="9">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>7</v>
@@ -5098,17 +5098,17 @@
         <v>21</v>
       </c>
       <c r="C25" s="9">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E25" s="7" t="str">
         <f>IFERROR(VLOOKUP(D25,Table1[#All],2,0),"")</f>
-        <v>Floculant</v>
+        <v>Sandios</v>
       </c>
       <c r="F25" s="7">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="G25" t="s">
         <v>25</v>
@@ -5119,17 +5119,17 @@
         <v>22</v>
       </c>
       <c r="C26" s="9">
-        <v>46267</v>
+        <v>46278</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="7" t="str">
         <f>IFERROR(VLOOKUP(D26,Table1[#All],2,0),"")</f>
-        <v>Kapur</v>
+        <v>Sandios</v>
       </c>
       <c r="F26" s="7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="G26" t="s">
         <v>25</v>
@@ -5140,17 +5140,17 @@
         <v>23</v>
       </c>
       <c r="C27" s="9">
-        <v>46268</v>
+        <v>46278</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E27" s="7" t="str">
         <f>IFERROR(VLOOKUP(D27,Table1[#All],2,0),"")</f>
-        <v>Kapur</v>
+        <v>Floculant</v>
       </c>
       <c r="F27" s="7">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="G27" t="s">
         <v>25</v>
@@ -5161,17 +5161,17 @@
         <v>24</v>
       </c>
       <c r="C28" s="9">
-        <v>46269</v>
+        <v>46280</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E28" s="7" t="str">
         <f>IFERROR(VLOOKUP(D28,Table1[#All],2,0),"")</f>
-        <v>Floculant</v>
+        <v>Sandios</v>
       </c>
       <c r="F28" s="7">
-        <v>25</v>
+        <v>450</v>
       </c>
       <c r="G28" t="s">
         <v>25</v>
@@ -5181,13 +5181,19 @@
       <c r="B29" s="8">
         <v>25</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
+      <c r="C29" s="9">
+        <v>46280</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="E29" s="7" t="str">
         <f>IFERROR(VLOOKUP(D29,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="7"/>
+        <v>Floculant</v>
+      </c>
+      <c r="F29" s="7">
+        <v>25</v>
+      </c>
       <c r="G29" t="s">
         <v>25</v>
       </c>
@@ -5196,10 +5202,19 @@
       <c r="B30" s="8">
         <v>26</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="C30" s="9">
+        <v>46283</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D30,Table1[#All],2,0),"")</f>
+        <v>Sandios</v>
+      </c>
+      <c r="F30" s="7">
+        <v>525</v>
+      </c>
       <c r="G30" t="s">
         <v>25</v>
       </c>
@@ -5208,10 +5223,19 @@
       <c r="B31" s="8">
         <v>27</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
+      <c r="C31" s="9">
+        <v>46283</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D31,Table1[#All],2,0),"")</f>
+        <v>Floculant</v>
+      </c>
+      <c r="F31" s="7">
+        <v>25</v>
+      </c>
       <c r="G31" t="s">
         <v>25</v>
       </c>
@@ -5220,9 +5244,12 @@
       <c r="B32" s="8">
         <v>28</v>
       </c>
-      <c r="C32" s="7"/>
+      <c r="C32" s="9"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
+      <c r="E32" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D32,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F32" s="7"/>
       <c r="G32" t="s">
         <v>25</v>
@@ -5232,9 +5259,12 @@
       <c r="B33" s="8">
         <v>29</v>
       </c>
-      <c r="C33" s="7"/>
+      <c r="C33" s="9"/>
       <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
+      <c r="E33" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D33,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F33" s="7"/>
       <c r="G33" t="s">
         <v>25</v>
@@ -5246,7 +5276,10 @@
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
+      <c r="E34" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D34,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F34" s="7"/>
       <c r="G34" t="s">
         <v>25</v>
@@ -5258,7 +5291,10 @@
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="E35" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D35,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F35" s="7"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
@@ -5267,7 +5303,10 @@
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
+      <c r="E36" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D36,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F36" s="7"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
@@ -5276,7 +5315,10 @@
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
+      <c r="E37" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D37,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F37" s="7"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
@@ -5285,7 +5327,10 @@
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
+      <c r="E38" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D38,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F38" s="7"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
@@ -5294,7 +5339,10 @@
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
+      <c r="E39" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D39,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F39" s="7"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
@@ -5303,7 +5351,10 @@
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
+      <c r="E40" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D40,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F40" s="7"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
@@ -5312,7 +5363,10 @@
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
+      <c r="E41" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D41,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F41" s="7"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
@@ -5321,7 +5375,10 @@
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
+      <c r="E42" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D42,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F42" s="7"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
@@ -5330,7 +5387,10 @@
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
+      <c r="E43" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D43,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F43" s="7"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
@@ -5339,7 +5399,10 @@
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
+      <c r="E44" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D44,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F44" s="7"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
@@ -5348,7 +5411,10 @@
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
+      <c r="E45" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D45,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F45" s="7"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
@@ -5357,7 +5423,10 @@
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
+      <c r="E46" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D46,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F46" s="7"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
@@ -5366,7 +5435,10 @@
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
+      <c r="E47" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D47,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F47" s="7"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
@@ -5375,7 +5447,10 @@
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
+      <c r="E48" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D48,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F48" s="7"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
@@ -5384,7 +5459,10 @@
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
+      <c r="E49" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D49,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F49" s="7"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
@@ -5393,7 +5471,10 @@
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
+      <c r="E50" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D50,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F50" s="7"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
@@ -5402,7 +5483,10 @@
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
+      <c r="E51" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D51,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F51" s="7"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
@@ -5411,7 +5495,10 @@
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
+      <c r="E52" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D52,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F52" s="7"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
@@ -5420,7 +5507,10 @@
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
+      <c r="E53" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D53,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F53" s="7"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
@@ -5429,7 +5519,10 @@
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
+      <c r="E54" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D54,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F54" s="7"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
@@ -5438,7 +5531,10 @@
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
+      <c r="E55" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D55,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F55" s="7"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
@@ -5447,7 +5543,10 @@
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
+      <c r="E56" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D56,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F56" s="7"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
@@ -5456,7 +5555,10 @@
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
+      <c r="E57" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D57,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F57" s="7"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
@@ -5465,7 +5567,10 @@
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
+      <c r="E58" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D58,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F58" s="7"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
@@ -5474,7 +5579,10 @@
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
+      <c r="E59" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D59,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F59" s="7"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
@@ -5483,7 +5591,10 @@
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
+      <c r="E60" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D60,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F60" s="7"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
@@ -5492,7 +5603,10 @@
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
+      <c r="E61" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D61,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F61" s="7"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
@@ -5501,7 +5615,10 @@
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
+      <c r="E62" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D62,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F62" s="7"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
@@ -5510,7 +5627,10 @@
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
+      <c r="E63" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D63,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F63" s="7"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
@@ -5519,7 +5639,10 @@
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
+      <c r="E64" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D64,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F64" s="7"/>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
@@ -5528,7 +5651,10 @@
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
+      <c r="E65" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D65,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F65" s="7"/>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
@@ -5537,7 +5663,10 @@
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
+      <c r="E66" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D66,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F66" s="7"/>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
@@ -5546,7 +5675,10 @@
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
+      <c r="E67" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D67,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F67" s="7"/>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
@@ -5555,7 +5687,10 @@
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
+      <c r="E68" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D68,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F68" s="7"/>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
@@ -5564,7 +5699,10 @@
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
+      <c r="E69" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D69,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F69" s="7"/>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
@@ -5573,7 +5711,10 @@
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
+      <c r="E70" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D70,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F70" s="7"/>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
@@ -5582,7 +5723,10 @@
       </c>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
+      <c r="E71" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D71,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F71" s="7"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
@@ -5591,7 +5735,10 @@
       </c>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
+      <c r="E72" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D72,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F72" s="7"/>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
@@ -5600,7 +5747,10 @@
       </c>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
+      <c r="E73" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D73,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F73" s="7"/>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
@@ -5609,7 +5759,10 @@
       </c>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
+      <c r="E74" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D74,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F74" s="7"/>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
@@ -5618,7 +5771,10 @@
       </c>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
+      <c r="E75" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D75,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F75" s="7"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
@@ -5627,7 +5783,10 @@
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
+      <c r="E76" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D76,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F76" s="7"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
@@ -5636,7 +5795,10 @@
       </c>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
+      <c r="E77" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D77,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F77" s="7"/>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
@@ -5645,7 +5807,10 @@
       </c>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
+      <c r="E78" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D78,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F78" s="7"/>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
@@ -5654,7 +5819,10 @@
       </c>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
+      <c r="E79" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D79,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F79" s="7"/>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
@@ -5663,7 +5831,10 @@
       </c>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
+      <c r="E80" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D80,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F80" s="7"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.3">
@@ -5672,7 +5843,10 @@
       </c>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
+      <c r="E81" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D81,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F81" s="7"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.3">
@@ -5681,7 +5855,10 @@
       </c>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
+      <c r="E82" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D82,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F82" s="7"/>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.3">
@@ -5690,7 +5867,10 @@
       </c>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
+      <c r="E83" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D83,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F83" s="7"/>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.3">
@@ -5699,7 +5879,10 @@
       </c>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
+      <c r="E84" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D84,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F84" s="7"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.3">
@@ -5708,7 +5891,10 @@
       </c>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
+      <c r="E85" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D85,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F85" s="7"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.3">
@@ -5717,7 +5903,10 @@
       </c>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
+      <c r="E86" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D86,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F86" s="7"/>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.3">
@@ -5726,7 +5915,10 @@
       </c>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
+      <c r="E87" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D87,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F87" s="7"/>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.3">
@@ -5735,7 +5927,10 @@
       </c>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
+      <c r="E88" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D88,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F88" s="7"/>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.3">
@@ -5744,7 +5939,10 @@
       </c>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
+      <c r="E89" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D89,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F89" s="7"/>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.3">
@@ -5753,7 +5951,10 @@
       </c>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
+      <c r="E90" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D90,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F90" s="7"/>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.3">
@@ -5762,7 +5963,10 @@
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
+      <c r="E91" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D91,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F91" s="7"/>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.3">
@@ -5771,7 +5975,10 @@
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
+      <c r="E92" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D92,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F92" s="7"/>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.3">
@@ -5780,7 +5987,10 @@
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
+      <c r="E93" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D93,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F93" s="7"/>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.3">
@@ -5789,7 +5999,10 @@
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
+      <c r="E94" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D94,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F94" s="7"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.3">
@@ -5798,7 +6011,10 @@
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
+      <c r="E95" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D95,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F95" s="7"/>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.3">
@@ -5807,7 +6023,10 @@
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
+      <c r="E96" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D96,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F96" s="7"/>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.3">
@@ -5816,7 +6035,10 @@
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
+      <c r="E97" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D97,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F97" s="7"/>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.3">
@@ -5825,7 +6047,10 @@
       </c>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
+      <c r="E98" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D98,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F98" s="7"/>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.3">
@@ -5834,7 +6059,10 @@
       </c>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
+      <c r="E99" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D99,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F99" s="7"/>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.3">
@@ -5843,7 +6071,10 @@
       </c>
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
+      <c r="E100" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D100,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F100" s="7"/>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.3">
@@ -5852,7 +6083,10 @@
       </c>
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
+      <c r="E101" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D101,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F101" s="7"/>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.3">
@@ -5861,7 +6095,10 @@
       </c>
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
+      <c r="E102" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D102,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F102" s="7"/>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.3">
@@ -5870,7 +6107,10 @@
       </c>
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
+      <c r="E103" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D103,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F103" s="7"/>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.3">
@@ -5879,7 +6119,10 @@
       </c>
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
+      <c r="E104" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D104,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F104" s="7"/>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.3">
@@ -5888,7 +6131,10 @@
       </c>
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
+      <c r="E105" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D105,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F105" s="7"/>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.3">
@@ -5897,7 +6143,10 @@
       </c>
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
+      <c r="E106" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D106,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F106" s="7"/>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.3">
@@ -5906,7 +6155,10 @@
       </c>
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
-      <c r="E107" s="7"/>
+      <c r="E107" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D107,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F107" s="7"/>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.3">
@@ -5915,7 +6167,10 @@
       </c>
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
+      <c r="E108" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D108,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F108" s="7"/>
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.3">
@@ -5924,7 +6179,10 @@
       </c>
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
+      <c r="E109" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D109,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F109" s="7"/>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.3">
@@ -5933,7 +6191,10 @@
       </c>
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
+      <c r="E110" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D110,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F110" s="7"/>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.3">
@@ -5942,7 +6203,10 @@
       </c>
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
+      <c r="E111" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D111,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F111" s="7"/>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.3">
@@ -5951,7 +6215,10 @@
       </c>
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
+      <c r="E112" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D112,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F112" s="7"/>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.3">
@@ -5960,7 +6227,10 @@
       </c>
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
+      <c r="E113" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D113,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F113" s="7"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.3">
@@ -5969,7 +6239,10 @@
       </c>
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
-      <c r="E114" s="7"/>
+      <c r="E114" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D114,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F114" s="7"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.3">
@@ -5978,7 +6251,10 @@
       </c>
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
+      <c r="E115" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D115,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F115" s="7"/>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.3">
@@ -5987,7 +6263,10 @@
       </c>
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
+      <c r="E116" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D116,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F116" s="7"/>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.3">
@@ -5996,7 +6275,10 @@
       </c>
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
+      <c r="E117" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D117,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F117" s="7"/>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.3">
@@ -6005,7 +6287,10 @@
       </c>
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
-      <c r="E118" s="7"/>
+      <c r="E118" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D118,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F118" s="7"/>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.3">
@@ -6014,7 +6299,10 @@
       </c>
       <c r="C119" s="7"/>
       <c r="D119" s="7"/>
-      <c r="E119" s="7"/>
+      <c r="E119" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D119,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F119" s="7"/>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.3">
@@ -6023,7 +6311,10 @@
       </c>
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
+      <c r="E120" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D120,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F120" s="7"/>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.3">
@@ -6032,7 +6323,10 @@
       </c>
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
+      <c r="E121" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D121,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F121" s="7"/>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
@@ -6041,7 +6335,10 @@
       </c>
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
+      <c r="E122" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D122,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F122" s="7"/>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
@@ -6050,7 +6347,10 @@
       </c>
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
+      <c r="E123" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D123,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F123" s="7"/>
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.3">
@@ -6059,7 +6359,10 @@
       </c>
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
+      <c r="E124" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D124,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F124" s="7"/>
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.3">
@@ -6068,7 +6371,10 @@
       </c>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
+      <c r="E125" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D125,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F125" s="7"/>
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.3">
@@ -6077,7 +6383,10 @@
       </c>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
+      <c r="E126" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D126,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F126" s="7"/>
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.3">
@@ -6086,7 +6395,10 @@
       </c>
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
+      <c r="E127" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D127,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F127" s="7"/>
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.3">
@@ -6095,7 +6407,10 @@
       </c>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
+      <c r="E128" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D128,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F128" s="7"/>
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.3">
@@ -6104,7 +6419,10 @@
       </c>
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
-      <c r="E129" s="7"/>
+      <c r="E129" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D129,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F129" s="7"/>
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.3">
@@ -6113,7 +6431,10 @@
       </c>
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
+      <c r="E130" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D130,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F130" s="7"/>
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.3">
@@ -6122,7 +6443,10 @@
       </c>
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
+      <c r="E131" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D131,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F131" s="7"/>
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.3">
@@ -6131,7 +6455,10 @@
       </c>
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
+      <c r="E132" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D132,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F132" s="7"/>
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.3">
@@ -6140,7 +6467,10 @@
       </c>
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
+      <c r="E133" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D133,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F133" s="7"/>
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.3">
@@ -6149,7 +6479,10 @@
       </c>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
+      <c r="E134" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D134,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F134" s="7"/>
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.3">
@@ -6158,7 +6491,10 @@
       </c>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
+      <c r="E135" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D135,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F135" s="7"/>
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.3">
@@ -6167,7 +6503,10 @@
       </c>
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
+      <c r="E136" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D136,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F136" s="7"/>
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.3">
@@ -6176,7 +6515,10 @@
       </c>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
+      <c r="E137" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D137,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F137" s="7"/>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.3">
@@ -6185,7 +6527,10 @@
       </c>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
+      <c r="E138" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D138,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F138" s="7"/>
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.3">
@@ -6194,7 +6539,10 @@
       </c>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
+      <c r="E139" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D139,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F139" s="7"/>
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.3">
@@ -6203,7 +6551,10 @@
       </c>
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
+      <c r="E140" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D140,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F140" s="7"/>
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.3">
@@ -6212,7 +6563,10 @@
       </c>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
-      <c r="E141" s="7"/>
+      <c r="E141" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D141,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F141" s="7"/>
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.3">
@@ -6221,7 +6575,10 @@
       </c>
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
-      <c r="E142" s="7"/>
+      <c r="E142" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D142,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F142" s="7"/>
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.3">
@@ -6230,7 +6587,10 @@
       </c>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
-      <c r="E143" s="7"/>
+      <c r="E143" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D143,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F143" s="7"/>
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.3">
@@ -6239,7 +6599,10 @@
       </c>
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
-      <c r="E144" s="7"/>
+      <c r="E144" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D144,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F144" s="7"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.3">
@@ -6248,7 +6611,10 @@
       </c>
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
-      <c r="E145" s="7"/>
+      <c r="E145" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D145,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F145" s="7"/>
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.3">
@@ -6257,7 +6623,10 @@
       </c>
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
+      <c r="E146" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D146,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F146" s="7"/>
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.3">
@@ -6266,7 +6635,10 @@
       </c>
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
+      <c r="E147" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D147,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F147" s="7"/>
     </row>
     <row r="148" spans="2:6" x14ac:dyDescent="0.3">
@@ -6275,7 +6647,10 @@
       </c>
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
-      <c r="E148" s="7"/>
+      <c r="E148" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D148,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F148" s="7"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.3">
@@ -6284,7 +6659,10 @@
       </c>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
-      <c r="E149" s="7"/>
+      <c r="E149" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D149,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F149" s="7"/>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.3">
@@ -6293,7 +6671,10 @@
       </c>
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
-      <c r="E150" s="7"/>
+      <c r="E150" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D150,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F150" s="7"/>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.3">
@@ -6302,7 +6683,10 @@
       </c>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
+      <c r="E151" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D151,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F151" s="7"/>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.3">
@@ -6311,7 +6695,10 @@
       </c>
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
+      <c r="E152" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D152,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F152" s="7"/>
     </row>
     <row r="153" spans="2:6" x14ac:dyDescent="0.3">
@@ -6320,7 +6707,10 @@
       </c>
       <c r="C153" s="7"/>
       <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
+      <c r="E153" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D153,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F153" s="7"/>
     </row>
     <row r="154" spans="2:6" x14ac:dyDescent="0.3">
@@ -6329,7 +6719,10 @@
       </c>
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
+      <c r="E154" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D154,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F154" s="7"/>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.3">
@@ -6338,7 +6731,10 @@
       </c>
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
+      <c r="E155" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D155,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F155" s="7"/>
     </row>
     <row r="156" spans="2:6" x14ac:dyDescent="0.3">
@@ -6347,7 +6743,10 @@
       </c>
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
+      <c r="E156" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D156,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F156" s="7"/>
     </row>
     <row r="157" spans="2:6" x14ac:dyDescent="0.3">
@@ -6356,7 +6755,10 @@
       </c>
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
+      <c r="E157" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D157,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F157" s="7"/>
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.3">
@@ -6365,7 +6767,10 @@
       </c>
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
+      <c r="E158" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D158,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F158" s="7"/>
     </row>
     <row r="159" spans="2:6" x14ac:dyDescent="0.3">
@@ -6374,7 +6779,10 @@
       </c>
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
-      <c r="E159" s="7"/>
+      <c r="E159" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D159,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F159" s="7"/>
     </row>
     <row r="160" spans="2:6" x14ac:dyDescent="0.3">
@@ -6383,7 +6791,10 @@
       </c>
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
-      <c r="E160" s="7"/>
+      <c r="E160" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D160,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F160" s="7"/>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.3">
@@ -6392,7 +6803,10 @@
       </c>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
-      <c r="E161" s="7"/>
+      <c r="E161" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D161,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F161" s="7"/>
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.3">
@@ -6401,7 +6815,10 @@
       </c>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
-      <c r="E162" s="7"/>
+      <c r="E162" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D162,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F162" s="7"/>
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.3">
@@ -6410,7 +6827,10 @@
       </c>
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
+      <c r="E163" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D163,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F163" s="7"/>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.3">
@@ -6419,7 +6839,10 @@
       </c>
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
-      <c r="E164" s="7"/>
+      <c r="E164" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D164,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F164" s="7"/>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.3">
@@ -6428,7 +6851,10 @@
       </c>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
+      <c r="E165" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D165,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F165" s="7"/>
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.3">
@@ -6437,7 +6863,10 @@
       </c>
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
+      <c r="E166" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D166,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F166" s="7"/>
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.3">
@@ -6446,7 +6875,10 @@
       </c>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
+      <c r="E167" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D167,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F167" s="7"/>
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.3">
@@ -6455,7 +6887,10 @@
       </c>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
-      <c r="E168" s="7"/>
+      <c r="E168" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D168,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F168" s="7"/>
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.3">
@@ -6464,7 +6899,10 @@
       </c>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
+      <c r="E169" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D169,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F169" s="7"/>
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.3">
@@ -6473,7 +6911,10 @@
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
-      <c r="E170" s="7"/>
+      <c r="E170" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D170,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F170" s="7"/>
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.3">
@@ -6482,7 +6923,10 @@
       </c>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
-      <c r="E171" s="7"/>
+      <c r="E171" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D171,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F171" s="7"/>
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.3">
@@ -6491,7 +6935,10 @@
       </c>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
-      <c r="E172" s="7"/>
+      <c r="E172" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D172,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F172" s="7"/>
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.3">
@@ -6500,7 +6947,10 @@
       </c>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
-      <c r="E173" s="7"/>
+      <c r="E173" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D173,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F173" s="7"/>
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.3">
@@ -6509,7 +6959,10 @@
       </c>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
-      <c r="E174" s="7"/>
+      <c r="E174" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D174,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F174" s="7"/>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.3">
@@ -6518,7 +6971,10 @@
       </c>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
+      <c r="E175" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D175,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F175" s="7"/>
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.3">
@@ -6527,7 +6983,10 @@
       </c>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
-      <c r="E176" s="7"/>
+      <c r="E176" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D176,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F176" s="7"/>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.3">
@@ -6536,7 +6995,10 @@
       </c>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
-      <c r="E177" s="7"/>
+      <c r="E177" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D177,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F177" s="7"/>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.3">
@@ -6545,7 +7007,10 @@
       </c>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
-      <c r="E178" s="7"/>
+      <c r="E178" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D178,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F178" s="7"/>
     </row>
     <row r="179" spans="2:6" x14ac:dyDescent="0.3">
@@ -6554,7 +7019,10 @@
       </c>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
+      <c r="E179" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D179,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F179" s="7"/>
     </row>
     <row r="180" spans="2:6" x14ac:dyDescent="0.3">
@@ -6563,7 +7031,10 @@
       </c>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
-      <c r="E180" s="7"/>
+      <c r="E180" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D180,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F180" s="7"/>
     </row>
     <row r="181" spans="2:6" x14ac:dyDescent="0.3">
@@ -6572,7 +7043,10 @@
       </c>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
-      <c r="E181" s="7"/>
+      <c r="E181" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D181,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F181" s="7"/>
     </row>
     <row r="182" spans="2:6" x14ac:dyDescent="0.3">
@@ -6581,7 +7055,10 @@
       </c>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
-      <c r="E182" s="7"/>
+      <c r="E182" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D182,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F182" s="7"/>
     </row>
     <row r="183" spans="2:6" x14ac:dyDescent="0.3">
@@ -6590,7 +7067,10 @@
       </c>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
-      <c r="E183" s="7"/>
+      <c r="E183" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D183,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F183" s="7"/>
     </row>
     <row r="184" spans="2:6" x14ac:dyDescent="0.3">
@@ -6599,7 +7079,10 @@
       </c>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
-      <c r="E184" s="7"/>
+      <c r="E184" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D184,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F184" s="7"/>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.3">
@@ -6608,7 +7091,10 @@
       </c>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
-      <c r="E185" s="7"/>
+      <c r="E185" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D185,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F185" s="7"/>
     </row>
     <row r="186" spans="2:6" x14ac:dyDescent="0.3">
@@ -6617,7 +7103,10 @@
       </c>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
-      <c r="E186" s="7"/>
+      <c r="E186" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D186,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F186" s="7"/>
     </row>
     <row r="187" spans="2:6" x14ac:dyDescent="0.3">
@@ -6626,7 +7115,10 @@
       </c>
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
-      <c r="E187" s="7"/>
+      <c r="E187" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D187,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F187" s="7"/>
     </row>
     <row r="188" spans="2:6" x14ac:dyDescent="0.3">
@@ -6635,7 +7127,10 @@
       </c>
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
-      <c r="E188" s="7"/>
+      <c r="E188" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D188,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F188" s="7"/>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.3">
@@ -6644,7 +7139,10 @@
       </c>
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
+      <c r="E189" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D189,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F189" s="7"/>
     </row>
     <row r="190" spans="2:6" x14ac:dyDescent="0.3">
@@ -6653,7 +7151,10 @@
       </c>
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
-      <c r="E190" s="7"/>
+      <c r="E190" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D190,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F190" s="7"/>
     </row>
     <row r="191" spans="2:6" x14ac:dyDescent="0.3">
@@ -6662,7 +7163,10 @@
       </c>
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
-      <c r="E191" s="7"/>
+      <c r="E191" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D191,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F191" s="7"/>
     </row>
     <row r="192" spans="2:6" x14ac:dyDescent="0.3">
@@ -6671,7 +7175,10 @@
       </c>
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
-      <c r="E192" s="7"/>
+      <c r="E192" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D192,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F192" s="7"/>
     </row>
     <row r="193" spans="2:6" x14ac:dyDescent="0.3">
@@ -6680,7 +7187,10 @@
       </c>
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
-      <c r="E193" s="7"/>
+      <c r="E193" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D193,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F193" s="7"/>
     </row>
     <row r="194" spans="2:6" x14ac:dyDescent="0.3">
@@ -6689,7 +7199,10 @@
       </c>
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
+      <c r="E194" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D194,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F194" s="7"/>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.3">
@@ -6698,7 +7211,10 @@
       </c>
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
-      <c r="E195" s="7"/>
+      <c r="E195" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D195,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F195" s="7"/>
     </row>
     <row r="196" spans="2:6" x14ac:dyDescent="0.3">
@@ -6707,7 +7223,10 @@
       </c>
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
-      <c r="E196" s="7"/>
+      <c r="E196" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D196,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F196" s="7"/>
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.3">
@@ -6716,7 +7235,10 @@
       </c>
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
-      <c r="E197" s="7"/>
+      <c r="E197" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D197,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F197" s="7"/>
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.3">
@@ -6725,7 +7247,10 @@
       </c>
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
-      <c r="E198" s="7"/>
+      <c r="E198" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D198,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F198" s="7"/>
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.3">
@@ -6734,7 +7259,10 @@
       </c>
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
-      <c r="E199" s="7"/>
+      <c r="E199" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D199,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F199" s="7"/>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.3">
@@ -6743,7 +7271,10 @@
       </c>
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
-      <c r="E200" s="7"/>
+      <c r="E200" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D200,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F200" s="7"/>
     </row>
     <row r="201" spans="2:6" x14ac:dyDescent="0.3">
@@ -6752,7 +7283,10 @@
       </c>
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
-      <c r="E201" s="7"/>
+      <c r="E201" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D201,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F201" s="7"/>
     </row>
     <row r="202" spans="2:6" x14ac:dyDescent="0.3">
@@ -6761,7 +7295,10 @@
       </c>
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
-      <c r="E202" s="7"/>
+      <c r="E202" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D202,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F202" s="7"/>
     </row>
     <row r="203" spans="2:6" x14ac:dyDescent="0.3">
@@ -6770,7 +7307,10 @@
       </c>
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
-      <c r="E203" s="7"/>
+      <c r="E203" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D203,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F203" s="7"/>
     </row>
     <row r="204" spans="2:6" x14ac:dyDescent="0.3">
@@ -6779,7 +7319,10 @@
       </c>
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
-      <c r="E204" s="7"/>
+      <c r="E204" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D204,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F204" s="7"/>
     </row>
     <row r="205" spans="2:6" x14ac:dyDescent="0.3">
@@ -6788,7 +7331,10 @@
       </c>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
-      <c r="E205" s="7"/>
+      <c r="E205" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D205,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F205" s="7"/>
     </row>
     <row r="206" spans="2:6" x14ac:dyDescent="0.3">
@@ -6797,7 +7343,10 @@
       </c>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
-      <c r="E206" s="7"/>
+      <c r="E206" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D206,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F206" s="7"/>
     </row>
     <row r="207" spans="2:6" x14ac:dyDescent="0.3">
@@ -6806,7 +7355,10 @@
       </c>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
-      <c r="E207" s="7"/>
+      <c r="E207" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D207,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F207" s="7"/>
     </row>
     <row r="208" spans="2:6" x14ac:dyDescent="0.3">
@@ -6815,7 +7367,10 @@
       </c>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
-      <c r="E208" s="7"/>
+      <c r="E208" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D208,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F208" s="7"/>
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.3">
@@ -6824,7 +7379,10 @@
       </c>
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
-      <c r="E209" s="7"/>
+      <c r="E209" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D209,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F209" s="7"/>
     </row>
     <row r="210" spans="2:6" x14ac:dyDescent="0.3">
@@ -6833,7 +7391,10 @@
       </c>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
-      <c r="E210" s="7"/>
+      <c r="E210" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D210,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F210" s="7"/>
     </row>
     <row r="211" spans="2:6" x14ac:dyDescent="0.3">
@@ -6842,7 +7403,10 @@
       </c>
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
-      <c r="E211" s="7"/>
+      <c r="E211" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D211,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F211" s="7"/>
     </row>
     <row r="212" spans="2:6" x14ac:dyDescent="0.3">
@@ -6851,7 +7415,10 @@
       </c>
       <c r="C212" s="7"/>
       <c r="D212" s="7"/>
-      <c r="E212" s="7"/>
+      <c r="E212" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D212,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F212" s="7"/>
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.3">
@@ -6860,7 +7427,10 @@
       </c>
       <c r="C213" s="7"/>
       <c r="D213" s="7"/>
-      <c r="E213" s="7"/>
+      <c r="E213" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D213,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F213" s="7"/>
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.3">
@@ -6869,7 +7439,10 @@
       </c>
       <c r="C214" s="7"/>
       <c r="D214" s="7"/>
-      <c r="E214" s="7"/>
+      <c r="E214" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D214,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F214" s="7"/>
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.3">
@@ -6878,7 +7451,10 @@
       </c>
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
-      <c r="E215" s="7"/>
+      <c r="E215" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D215,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F215" s="7"/>
     </row>
     <row r="216" spans="2:6" x14ac:dyDescent="0.3">
@@ -6887,7 +7463,10 @@
       </c>
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
-      <c r="E216" s="7"/>
+      <c r="E216" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D216,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F216" s="7"/>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.3">
@@ -6896,7 +7475,10 @@
       </c>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
-      <c r="E217" s="7"/>
+      <c r="E217" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D217,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F217" s="7"/>
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.3">
@@ -6905,7 +7487,10 @@
       </c>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
-      <c r="E218" s="7"/>
+      <c r="E218" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D218,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F218" s="7"/>
     </row>
     <row r="219" spans="2:6" x14ac:dyDescent="0.3">
@@ -6914,7 +7499,10 @@
       </c>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
-      <c r="E219" s="7"/>
+      <c r="E219" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D219,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F219" s="7"/>
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.3">
@@ -6923,7 +7511,10 @@
       </c>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
-      <c r="E220" s="7"/>
+      <c r="E220" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D220,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F220" s="7"/>
     </row>
     <row r="221" spans="2:6" x14ac:dyDescent="0.3">
@@ -6932,7 +7523,10 @@
       </c>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
-      <c r="E221" s="7"/>
+      <c r="E221" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D221,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F221" s="7"/>
     </row>
     <row r="222" spans="2:6" x14ac:dyDescent="0.3">
@@ -6941,7 +7535,10 @@
       </c>
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
-      <c r="E222" s="7"/>
+      <c r="E222" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D222,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F222" s="7"/>
     </row>
     <row r="223" spans="2:6" x14ac:dyDescent="0.3">
@@ -6950,7 +7547,10 @@
       </c>
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
-      <c r="E223" s="7"/>
+      <c r="E223" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D223,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F223" s="7"/>
     </row>
     <row r="224" spans="2:6" x14ac:dyDescent="0.3">
@@ -6959,7 +7559,10 @@
       </c>
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
-      <c r="E224" s="7"/>
+      <c r="E224" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D224,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F224" s="7"/>
     </row>
     <row r="225" spans="2:6" x14ac:dyDescent="0.3">
@@ -6968,7 +7571,10 @@
       </c>
       <c r="C225" s="7"/>
       <c r="D225" s="7"/>
-      <c r="E225" s="7"/>
+      <c r="E225" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D225,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F225" s="7"/>
     </row>
     <row r="226" spans="2:6" x14ac:dyDescent="0.3">
@@ -6977,7 +7583,10 @@
       </c>
       <c r="C226" s="7"/>
       <c r="D226" s="7"/>
-      <c r="E226" s="7"/>
+      <c r="E226" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D226,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F226" s="7"/>
     </row>
     <row r="227" spans="2:6" x14ac:dyDescent="0.3">
@@ -6986,7 +7595,10 @@
       </c>
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
-      <c r="E227" s="7"/>
+      <c r="E227" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D227,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F227" s="7"/>
     </row>
     <row r="228" spans="2:6" x14ac:dyDescent="0.3">
@@ -6995,7 +7607,10 @@
       </c>
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
-      <c r="E228" s="7"/>
+      <c r="E228" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D228,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F228" s="7"/>
     </row>
     <row r="229" spans="2:6" x14ac:dyDescent="0.3">
@@ -7004,7 +7619,10 @@
       </c>
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
-      <c r="E229" s="7"/>
+      <c r="E229" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D229,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F229" s="7"/>
     </row>
     <row r="230" spans="2:6" x14ac:dyDescent="0.3">
@@ -7013,7 +7631,10 @@
       </c>
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
-      <c r="E230" s="7"/>
+      <c r="E230" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D230,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F230" s="7"/>
     </row>
     <row r="231" spans="2:6" x14ac:dyDescent="0.3">
@@ -7022,7 +7643,10 @@
       </c>
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
-      <c r="E231" s="7"/>
+      <c r="E231" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D231,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F231" s="7"/>
     </row>
     <row r="232" spans="2:6" x14ac:dyDescent="0.3">
@@ -7031,7 +7655,10 @@
       </c>
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
-      <c r="E232" s="7"/>
+      <c r="E232" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D232,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F232" s="7"/>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.3">
@@ -7040,7 +7667,10 @@
       </c>
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
-      <c r="E233" s="7"/>
+      <c r="E233" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D233,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F233" s="7"/>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.3">
@@ -7049,7 +7679,10 @@
       </c>
       <c r="C234" s="7"/>
       <c r="D234" s="7"/>
-      <c r="E234" s="7"/>
+      <c r="E234" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D234,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F234" s="7"/>
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.3">
@@ -7058,7 +7691,10 @@
       </c>
       <c r="C235" s="7"/>
       <c r="D235" s="7"/>
-      <c r="E235" s="7"/>
+      <c r="E235" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D235,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F235" s="7"/>
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.3">
@@ -7067,7 +7703,10 @@
       </c>
       <c r="C236" s="7"/>
       <c r="D236" s="7"/>
-      <c r="E236" s="7"/>
+      <c r="E236" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D236,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F236" s="7"/>
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.3">
@@ -7076,7 +7715,10 @@
       </c>
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
-      <c r="E237" s="7"/>
+      <c r="E237" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D237,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F237" s="7"/>
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.3">
@@ -7085,7 +7727,10 @@
       </c>
       <c r="C238" s="7"/>
       <c r="D238" s="7"/>
-      <c r="E238" s="7"/>
+      <c r="E238" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D238,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F238" s="7"/>
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.3">
@@ -7094,7 +7739,10 @@
       </c>
       <c r="C239" s="7"/>
       <c r="D239" s="7"/>
-      <c r="E239" s="7"/>
+      <c r="E239" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D239,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F239" s="7"/>
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.3">
@@ -7103,7 +7751,10 @@
       </c>
       <c r="C240" s="7"/>
       <c r="D240" s="7"/>
-      <c r="E240" s="7"/>
+      <c r="E240" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D240,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F240" s="7"/>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.3">
@@ -7112,7 +7763,10 @@
       </c>
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
-      <c r="E241" s="7"/>
+      <c r="E241" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D241,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F241" s="7"/>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.3">
@@ -7121,7 +7775,10 @@
       </c>
       <c r="C242" s="7"/>
       <c r="D242" s="7"/>
-      <c r="E242" s="7"/>
+      <c r="E242" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D242,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F242" s="7"/>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.3">
@@ -7130,7 +7787,10 @@
       </c>
       <c r="C243" s="7"/>
       <c r="D243" s="7"/>
-      <c r="E243" s="7"/>
+      <c r="E243" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D243,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F243" s="7"/>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.3">
@@ -7139,7 +7799,10 @@
       </c>
       <c r="C244" s="7"/>
       <c r="D244" s="7"/>
-      <c r="E244" s="7"/>
+      <c r="E244" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D244,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F244" s="7"/>
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.3">
@@ -7148,7 +7811,10 @@
       </c>
       <c r="C245" s="7"/>
       <c r="D245" s="7"/>
-      <c r="E245" s="7"/>
+      <c r="E245" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D245,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F245" s="7"/>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.3">
@@ -7157,7 +7823,10 @@
       </c>
       <c r="C246" s="7"/>
       <c r="D246" s="7"/>
-      <c r="E246" s="7"/>
+      <c r="E246" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D246,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F246" s="7"/>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.3">
@@ -7166,7 +7835,10 @@
       </c>
       <c r="C247" s="7"/>
       <c r="D247" s="7"/>
-      <c r="E247" s="7"/>
+      <c r="E247" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D247,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F247" s="7"/>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.3">
@@ -7175,7 +7847,10 @@
       </c>
       <c r="C248" s="7"/>
       <c r="D248" s="7"/>
-      <c r="E248" s="7"/>
+      <c r="E248" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D248,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F248" s="7"/>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.3">
@@ -7184,7 +7859,10 @@
       </c>
       <c r="C249" s="7"/>
       <c r="D249" s="7"/>
-      <c r="E249" s="7"/>
+      <c r="E249" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D249,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F249" s="7"/>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.3">
@@ -7193,7 +7871,10 @@
       </c>
       <c r="C250" s="7"/>
       <c r="D250" s="7"/>
-      <c r="E250" s="7"/>
+      <c r="E250" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D250,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F250" s="7"/>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.3">
@@ -7202,7 +7883,10 @@
       </c>
       <c r="C251" s="7"/>
       <c r="D251" s="7"/>
-      <c r="E251" s="7"/>
+      <c r="E251" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D251,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F251" s="7"/>
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.3">
@@ -7211,7 +7895,10 @@
       </c>
       <c r="C252" s="7"/>
       <c r="D252" s="7"/>
-      <c r="E252" s="7"/>
+      <c r="E252" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D252,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F252" s="7"/>
     </row>
     <row r="253" spans="2:6" x14ac:dyDescent="0.3">
@@ -7220,7 +7907,10 @@
       </c>
       <c r="C253" s="7"/>
       <c r="D253" s="7"/>
-      <c r="E253" s="7"/>
+      <c r="E253" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D253,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F253" s="7"/>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.3">
@@ -7229,7 +7919,10 @@
       </c>
       <c r="C254" s="7"/>
       <c r="D254" s="7"/>
-      <c r="E254" s="7"/>
+      <c r="E254" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D254,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F254" s="7"/>
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.3">
@@ -7238,7 +7931,10 @@
       </c>
       <c r="C255" s="7"/>
       <c r="D255" s="7"/>
-      <c r="E255" s="7"/>
+      <c r="E255" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D255,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F255" s="7"/>
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.3">
@@ -7247,7 +7943,10 @@
       </c>
       <c r="C256" s="7"/>
       <c r="D256" s="7"/>
-      <c r="E256" s="7"/>
+      <c r="E256" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D256,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F256" s="7"/>
     </row>
     <row r="257" spans="2:6" x14ac:dyDescent="0.3">
@@ -7256,7 +7955,10 @@
       </c>
       <c r="C257" s="7"/>
       <c r="D257" s="7"/>
-      <c r="E257" s="7"/>
+      <c r="E257" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D257,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F257" s="7"/>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.3">
@@ -7265,7 +7967,10 @@
       </c>
       <c r="C258" s="7"/>
       <c r="D258" s="7"/>
-      <c r="E258" s="7"/>
+      <c r="E258" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D258,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F258" s="7"/>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.3">
@@ -7274,7 +7979,10 @@
       </c>
       <c r="C259" s="7"/>
       <c r="D259" s="7"/>
-      <c r="E259" s="7"/>
+      <c r="E259" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D259,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F259" s="7"/>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.3">
@@ -7283,7 +7991,10 @@
       </c>
       <c r="C260" s="7"/>
       <c r="D260" s="7"/>
-      <c r="E260" s="7"/>
+      <c r="E260" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D260,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F260" s="7"/>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.3">
@@ -7292,7 +8003,10 @@
       </c>
       <c r="C261" s="7"/>
       <c r="D261" s="7"/>
-      <c r="E261" s="7"/>
+      <c r="E261" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D261,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F261" s="7"/>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.3">
@@ -7301,7 +8015,10 @@
       </c>
       <c r="C262" s="7"/>
       <c r="D262" s="7"/>
-      <c r="E262" s="7"/>
+      <c r="E262" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D262,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F262" s="7"/>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.3">
@@ -7310,7 +8027,10 @@
       </c>
       <c r="C263" s="7"/>
       <c r="D263" s="7"/>
-      <c r="E263" s="7"/>
+      <c r="E263" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D263,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F263" s="7"/>
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.3">
@@ -7319,7 +8039,10 @@
       </c>
       <c r="C264" s="7"/>
       <c r="D264" s="7"/>
-      <c r="E264" s="7"/>
+      <c r="E264" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D264,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F264" s="7"/>
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.3">
@@ -7328,7 +8051,10 @@
       </c>
       <c r="C265" s="7"/>
       <c r="D265" s="7"/>
-      <c r="E265" s="7"/>
+      <c r="E265" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D265,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F265" s="7"/>
     </row>
     <row r="266" spans="2:6" x14ac:dyDescent="0.3">
@@ -7337,7 +8063,10 @@
       </c>
       <c r="C266" s="7"/>
       <c r="D266" s="7"/>
-      <c r="E266" s="7"/>
+      <c r="E266" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D266,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F266" s="7"/>
     </row>
     <row r="267" spans="2:6" x14ac:dyDescent="0.3">
@@ -7346,7 +8075,10 @@
       </c>
       <c r="C267" s="7"/>
       <c r="D267" s="7"/>
-      <c r="E267" s="7"/>
+      <c r="E267" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D267,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F267" s="7"/>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.3">
@@ -7355,7 +8087,10 @@
       </c>
       <c r="C268" s="7"/>
       <c r="D268" s="7"/>
-      <c r="E268" s="7"/>
+      <c r="E268" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D268,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F268" s="7"/>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.3">
@@ -7364,7 +8099,10 @@
       </c>
       <c r="C269" s="7"/>
       <c r="D269" s="7"/>
-      <c r="E269" s="7"/>
+      <c r="E269" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D269,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F269" s="7"/>
     </row>
     <row r="270" spans="2:6" x14ac:dyDescent="0.3">
@@ -7373,7 +8111,10 @@
       </c>
       <c r="C270" s="7"/>
       <c r="D270" s="7"/>
-      <c r="E270" s="7"/>
+      <c r="E270" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D270,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F270" s="7"/>
     </row>
     <row r="271" spans="2:6" x14ac:dyDescent="0.3">
@@ -7382,7 +8123,10 @@
       </c>
       <c r="C271" s="7"/>
       <c r="D271" s="7"/>
-      <c r="E271" s="7"/>
+      <c r="E271" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D271,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F271" s="7"/>
     </row>
     <row r="272" spans="2:6" x14ac:dyDescent="0.3">
@@ -7391,7 +8135,10 @@
       </c>
       <c r="C272" s="7"/>
       <c r="D272" s="7"/>
-      <c r="E272" s="7"/>
+      <c r="E272" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D272,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F272" s="7"/>
     </row>
     <row r="273" spans="2:6" x14ac:dyDescent="0.3">
@@ -7400,7 +8147,10 @@
       </c>
       <c r="C273" s="7"/>
       <c r="D273" s="7"/>
-      <c r="E273" s="7"/>
+      <c r="E273" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D273,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F273" s="7"/>
     </row>
     <row r="274" spans="2:6" x14ac:dyDescent="0.3">
@@ -7409,7 +8159,10 @@
       </c>
       <c r="C274" s="7"/>
       <c r="D274" s="7"/>
-      <c r="E274" s="7"/>
+      <c r="E274" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D274,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F274" s="7"/>
     </row>
     <row r="275" spans="2:6" x14ac:dyDescent="0.3">
@@ -7418,7 +8171,10 @@
       </c>
       <c r="C275" s="7"/>
       <c r="D275" s="7"/>
-      <c r="E275" s="7"/>
+      <c r="E275" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D275,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F275" s="7"/>
     </row>
     <row r="276" spans="2:6" x14ac:dyDescent="0.3">
@@ -7427,7 +8183,10 @@
       </c>
       <c r="C276" s="7"/>
       <c r="D276" s="7"/>
-      <c r="E276" s="7"/>
+      <c r="E276" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D276,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F276" s="7"/>
     </row>
     <row r="277" spans="2:6" x14ac:dyDescent="0.3">
@@ -7436,7 +8195,10 @@
       </c>
       <c r="C277" s="7"/>
       <c r="D277" s="7"/>
-      <c r="E277" s="7"/>
+      <c r="E277" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D277,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F277" s="7"/>
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.3">
@@ -7445,7 +8207,10 @@
       </c>
       <c r="C278" s="7"/>
       <c r="D278" s="7"/>
-      <c r="E278" s="7"/>
+      <c r="E278" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D278,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F278" s="7"/>
     </row>
     <row r="279" spans="2:6" x14ac:dyDescent="0.3">
@@ -7454,7 +8219,10 @@
       </c>
       <c r="C279" s="7"/>
       <c r="D279" s="7"/>
-      <c r="E279" s="7"/>
+      <c r="E279" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D279,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F279" s="7"/>
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.3">
@@ -7463,7 +8231,10 @@
       </c>
       <c r="C280" s="7"/>
       <c r="D280" s="7"/>
-      <c r="E280" s="7"/>
+      <c r="E280" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D280,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F280" s="7"/>
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.3">
@@ -7472,7 +8243,10 @@
       </c>
       <c r="C281" s="7"/>
       <c r="D281" s="7"/>
-      <c r="E281" s="7"/>
+      <c r="E281" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D281,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F281" s="7"/>
     </row>
     <row r="282" spans="2:6" x14ac:dyDescent="0.3">
@@ -7481,7 +8255,10 @@
       </c>
       <c r="C282" s="7"/>
       <c r="D282" s="7"/>
-      <c r="E282" s="7"/>
+      <c r="E282" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D282,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F282" s="7"/>
     </row>
     <row r="283" spans="2:6" x14ac:dyDescent="0.3">
@@ -7490,7 +8267,10 @@
       </c>
       <c r="C283" s="7"/>
       <c r="D283" s="7"/>
-      <c r="E283" s="7"/>
+      <c r="E283" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D283,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F283" s="7"/>
     </row>
     <row r="284" spans="2:6" x14ac:dyDescent="0.3">
@@ -7499,7 +8279,10 @@
       </c>
       <c r="C284" s="7"/>
       <c r="D284" s="7"/>
-      <c r="E284" s="7"/>
+      <c r="E284" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D284,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F284" s="7"/>
     </row>
     <row r="285" spans="2:6" x14ac:dyDescent="0.3">
@@ -7508,7 +8291,10 @@
       </c>
       <c r="C285" s="7"/>
       <c r="D285" s="7"/>
-      <c r="E285" s="7"/>
+      <c r="E285" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D285,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F285" s="7"/>
     </row>
     <row r="286" spans="2:6" x14ac:dyDescent="0.3">
@@ -7517,7 +8303,10 @@
       </c>
       <c r="C286" s="7"/>
       <c r="D286" s="7"/>
-      <c r="E286" s="7"/>
+      <c r="E286" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D286,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F286" s="7"/>
     </row>
     <row r="287" spans="2:6" x14ac:dyDescent="0.3">
@@ -7526,7 +8315,10 @@
       </c>
       <c r="C287" s="7"/>
       <c r="D287" s="7"/>
-      <c r="E287" s="7"/>
+      <c r="E287" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D287,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F287" s="7"/>
     </row>
     <row r="288" spans="2:6" x14ac:dyDescent="0.3">
@@ -7535,7 +8327,10 @@
       </c>
       <c r="C288" s="7"/>
       <c r="D288" s="7"/>
-      <c r="E288" s="7"/>
+      <c r="E288" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D288,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F288" s="7"/>
     </row>
     <row r="289" spans="2:6" x14ac:dyDescent="0.3">
@@ -7544,7 +8339,10 @@
       </c>
       <c r="C289" s="7"/>
       <c r="D289" s="7"/>
-      <c r="E289" s="7"/>
+      <c r="E289" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D289,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F289" s="7"/>
     </row>
     <row r="290" spans="2:6" x14ac:dyDescent="0.3">
@@ -7553,7 +8351,10 @@
       </c>
       <c r="C290" s="7"/>
       <c r="D290" s="7"/>
-      <c r="E290" s="7"/>
+      <c r="E290" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D290,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F290" s="7"/>
     </row>
     <row r="291" spans="2:6" x14ac:dyDescent="0.3">
@@ -7562,7 +8363,10 @@
       </c>
       <c r="C291" s="7"/>
       <c r="D291" s="7"/>
-      <c r="E291" s="7"/>
+      <c r="E291" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D291,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F291" s="7"/>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.3">
@@ -7571,7 +8375,10 @@
       </c>
       <c r="C292" s="7"/>
       <c r="D292" s="7"/>
-      <c r="E292" s="7"/>
+      <c r="E292" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D292,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F292" s="7"/>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.3">
@@ -7580,7 +8387,10 @@
       </c>
       <c r="C293" s="7"/>
       <c r="D293" s="7"/>
-      <c r="E293" s="7"/>
+      <c r="E293" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D293,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F293" s="7"/>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.3">
@@ -7589,7 +8399,10 @@
       </c>
       <c r="C294" s="7"/>
       <c r="D294" s="7"/>
-      <c r="E294" s="7"/>
+      <c r="E294" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D294,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F294" s="7"/>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.3">
@@ -7598,7 +8411,10 @@
       </c>
       <c r="C295" s="7"/>
       <c r="D295" s="7"/>
-      <c r="E295" s="7"/>
+      <c r="E295" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D295,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F295" s="7"/>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.3">
@@ -7607,7 +8423,10 @@
       </c>
       <c r="C296" s="7"/>
       <c r="D296" s="7"/>
-      <c r="E296" s="7"/>
+      <c r="E296" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D296,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F296" s="7"/>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.3">
@@ -7616,7 +8435,10 @@
       </c>
       <c r="C297" s="7"/>
       <c r="D297" s="7"/>
-      <c r="E297" s="7"/>
+      <c r="E297" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D297,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F297" s="7"/>
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.3">
@@ -7625,7 +8447,10 @@
       </c>
       <c r="C298" s="7"/>
       <c r="D298" s="7"/>
-      <c r="E298" s="7"/>
+      <c r="E298" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D298,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F298" s="7"/>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.3">
@@ -7634,7 +8459,10 @@
       </c>
       <c r="C299" s="7"/>
       <c r="D299" s="7"/>
-      <c r="E299" s="7"/>
+      <c r="E299" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D299,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F299" s="7"/>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.3">
@@ -7643,7 +8471,10 @@
       </c>
       <c r="C300" s="7"/>
       <c r="D300" s="7"/>
-      <c r="E300" s="7"/>
+      <c r="E300" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D300,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F300" s="7"/>
     </row>
     <row r="301" spans="2:6" x14ac:dyDescent="0.3">
@@ -7652,7 +8483,10 @@
       </c>
       <c r="C301" s="7"/>
       <c r="D301" s="7"/>
-      <c r="E301" s="7"/>
+      <c r="E301" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D301,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F301" s="7"/>
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.3">
@@ -7661,7 +8495,10 @@
       </c>
       <c r="C302" s="7"/>
       <c r="D302" s="7"/>
-      <c r="E302" s="7"/>
+      <c r="E302" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D302,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F302" s="7"/>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.3">
@@ -7670,7 +8507,10 @@
       </c>
       <c r="C303" s="7"/>
       <c r="D303" s="7"/>
-      <c r="E303" s="7"/>
+      <c r="E303" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D303,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F303" s="7"/>
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.3">
@@ -7679,7 +8519,10 @@
       </c>
       <c r="C304" s="7"/>
       <c r="D304" s="7"/>
-      <c r="E304" s="7"/>
+      <c r="E304" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D304,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F304" s="7"/>
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.3">
@@ -7688,7 +8531,10 @@
       </c>
       <c r="C305" s="7"/>
       <c r="D305" s="7"/>
-      <c r="E305" s="7"/>
+      <c r="E305" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D305,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F305" s="7"/>
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.3">
@@ -7697,7 +8543,10 @@
       </c>
       <c r="C306" s="7"/>
       <c r="D306" s="7"/>
-      <c r="E306" s="7"/>
+      <c r="E306" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D306,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F306" s="7"/>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.3">
@@ -7706,7 +8555,10 @@
       </c>
       <c r="C307" s="7"/>
       <c r="D307" s="7"/>
-      <c r="E307" s="7"/>
+      <c r="E307" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D307,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F307" s="7"/>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.3">
@@ -7715,7 +8567,10 @@
       </c>
       <c r="C308" s="7"/>
       <c r="D308" s="7"/>
-      <c r="E308" s="7"/>
+      <c r="E308" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D308,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F308" s="7"/>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.3">
@@ -7724,7 +8579,10 @@
       </c>
       <c r="C309" s="7"/>
       <c r="D309" s="7"/>
-      <c r="E309" s="7"/>
+      <c r="E309" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D309,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F309" s="7"/>
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.3">
@@ -7733,7 +8591,10 @@
       </c>
       <c r="C310" s="7"/>
       <c r="D310" s="7"/>
-      <c r="E310" s="7"/>
+      <c r="E310" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D310,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F310" s="7"/>
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.3">
@@ -7742,7 +8603,10 @@
       </c>
       <c r="C311" s="7"/>
       <c r="D311" s="7"/>
-      <c r="E311" s="7"/>
+      <c r="E311" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D311,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F311" s="7"/>
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.3">
@@ -7751,7 +8615,10 @@
       </c>
       <c r="C312" s="7"/>
       <c r="D312" s="7"/>
-      <c r="E312" s="7"/>
+      <c r="E312" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D312,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F312" s="7"/>
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.3">
@@ -7760,7 +8627,10 @@
       </c>
       <c r="C313" s="7"/>
       <c r="D313" s="7"/>
-      <c r="E313" s="7"/>
+      <c r="E313" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D313,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F313" s="7"/>
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.3">
@@ -7769,7 +8639,10 @@
       </c>
       <c r="C314" s="7"/>
       <c r="D314" s="7"/>
-      <c r="E314" s="7"/>
+      <c r="E314" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D314,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F314" s="7"/>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.3">
@@ -7778,7 +8651,10 @@
       </c>
       <c r="C315" s="7"/>
       <c r="D315" s="7"/>
-      <c r="E315" s="7"/>
+      <c r="E315" s="7" t="str">
+        <f>IFERROR(VLOOKUP(D315,Table1[#All],2,0),"")</f>
+        <v/>
+      </c>
       <c r="F315" s="7"/>
     </row>
   </sheetData>
@@ -7795,7 +8671,7 @@
           <x14:formula1>
             <xm:f>'Stock Barang'!$B$4:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D5:D29</xm:sqref>
+          <xm:sqref>D5:D315</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Reagent Usage dan Stock Reagent.xlsx
+++ b/Reagent Usage dan Stock Reagent.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramda\Documents\Zeta_Edit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC2ADA7-55B6-4A5C-80AD-B0C43FB76B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35211DD-B11A-41BB-BA0B-30515A939761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{44BE0AC2-6033-44C2-8356-2F41A96EBF2E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44BE0AC2-6033-44C2-8356-2F41A96EBF2E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Barang Masuk" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
-    <sheet name="Stock Barang" sheetId="1" r:id="rId3"/>
-    <sheet name="Barang Keluar " sheetId="3" r:id="rId4"/>
+    <sheet name="Stock Barang" sheetId="1" r:id="rId1"/>
+    <sheet name="Barang Masuk" sheetId="2" r:id="rId2"/>
+    <sheet name="Barang Keluar " sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -93,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="34">
   <si>
     <t>No</t>
   </si>
@@ -388,62 +387,6 @@
   </cellStyles>
   <dxfs count="15">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -490,6 +433,32 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -602,6 +571,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -624,13 +600,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -667,6 +636,36 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -687,22 +686,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1AC36863-5F67-4496-A2C7-808F86C284A1}" name="Table1" displayName="Table1" ref="B3:H21" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1AC36863-5F67-4496-A2C7-808F86C284A1}" name="Table1" displayName="Table1" ref="B3:H21" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
   <autoFilter ref="B3:H21" xr:uid="{1AC36863-5F67-4496-A2C7-808F86C284A1}"/>
   <tableColumns count="7">
-    <tableColumn id="2" xr3:uid="{E78837C8-954C-440F-BCB4-114AA4EBC159}" name="Kode Barang" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{BB8DB245-EB50-4D84-9B3E-D2CF46896708}" name="Nama Barang" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{36BAEBBD-D2E7-42F0-B8AF-873903FEFEA9}" name="Stok Awal " dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{3DA331B5-0C1B-4517-AC2B-660041411D0B}" name="Barang Masuk" dataDxfId="6">
+    <tableColumn id="2" xr3:uid="{E78837C8-954C-440F-BCB4-114AA4EBC159}" name="Kode Barang" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{BB8DB245-EB50-4D84-9B3E-D2CF46896708}" name="Nama Barang" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{36BAEBBD-D2E7-42F0-B8AF-873903FEFEA9}" name="Stok Awal " dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{3DA331B5-0C1B-4517-AC2B-660041411D0B}" name="Barang Masuk" dataDxfId="3">
       <calculatedColumnFormula>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4231B6CF-326F-44B2-8A60-3DCCDB55861D}" name="Barang Keluar " dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{4231B6CF-326F-44B2-8A60-3DCCDB55861D}" name="Barang Keluar " dataDxfId="2">
       <calculatedColumnFormula>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{9472852C-4AF5-44FD-A6F5-E9EDEDD511AE}" name="Stock Akhir" dataDxfId="5">
+    <tableColumn id="7" xr3:uid="{9472852C-4AF5-44FD-A6F5-E9EDEDD511AE}" name="Stock Akhir" dataDxfId="1">
       <calculatedColumnFormula>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{C780F2FB-0F97-426F-AC7D-196550D5A9CF}" name="Satuan" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{C780F2FB-0F97-426F-AC7D-196550D5A9CF}" name="Satuan" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1044,6 +1043,476 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CAC8830-268B-489B-9A12-01936A5CA5A2}">
+  <dimension ref="B1:H21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="B1" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2">
+        <v>150</v>
+      </c>
+      <c r="E4" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>150</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E5" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>3000</v>
+      </c>
+      <c r="G5" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>2000</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5750</v>
+      </c>
+      <c r="E6" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>3725</v>
+      </c>
+      <c r="G6" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>2025</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2">
+        <v>7500</v>
+      </c>
+      <c r="E7" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>5000</v>
+      </c>
+      <c r="F7" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>3000</v>
+      </c>
+      <c r="G7" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>9500</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2">
+        <v>400</v>
+      </c>
+      <c r="E8" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>250</v>
+      </c>
+      <c r="F8" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>650</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="2">
+        <v>125</v>
+      </c>
+      <c r="E10" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>375</v>
+      </c>
+      <c r="F10" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="13">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>500</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2">
+        <v>14975</v>
+      </c>
+      <c r="E11" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>14975</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2">
+        <v>6425</v>
+      </c>
+      <c r="E12" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>6225</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="12"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="2">
+        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="15">
+        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="greaterThan">
+      <formula>3999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G10">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="greaterThan">
+      <formula>500</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="lessThan">
+      <formula>500</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E498DA0C-37B1-4354-B038-CA23BB50DFD0}">
   <dimension ref="B4:F334"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1093,25 +1562,37 @@
       <c r="B6" s="8">
         <v>2</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="7"/>
+      <c r="C6" s="9">
+        <v>46285</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="E6" s="7" t="str">
         <f>IFERROR(VLOOKUP(D6,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="7"/>
+        <v>HCL</v>
+      </c>
+      <c r="F6" s="7">
+        <v>375</v>
+      </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="8">
         <v>3</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+      <c r="C7" s="9">
+        <v>46285</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E7" s="7" t="str">
         <f>IFERROR(VLOOKUP(D7,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F7" s="7"/>
+        <v>Kaustik</v>
+      </c>
+      <c r="F7" s="7">
+        <v>250</v>
+      </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="8">
@@ -4145,486 +4626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{684DB87B-F02C-41BA-A196-5B8F96176BFB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CAC8830-268B-489B-9A12-01936A5CA5A2}">
-  <dimension ref="B1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" style="10" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="B1" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2">
-        <v>150</v>
-      </c>
-      <c r="E4" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>150</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2">
-        <v>5000</v>
-      </c>
-      <c r="E5" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>3000</v>
-      </c>
-      <c r="G5" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>2000</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2">
-        <v>5750</v>
-      </c>
-      <c r="E6" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>3725</v>
-      </c>
-      <c r="G6" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>2025</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2">
-        <v>7500</v>
-      </c>
-      <c r="E7" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>5000</v>
-      </c>
-      <c r="F7" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>3000</v>
-      </c>
-      <c r="G7" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>9500</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="2">
-        <v>400</v>
-      </c>
-      <c r="E8" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>400</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="2">
-        <v>125</v>
-      </c>
-      <c r="E10" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="13">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>125</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="2">
-        <v>14975</v>
-      </c>
-      <c r="E11" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>14975</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="2">
-        <v>6425</v>
-      </c>
-      <c r="E12" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>200</v>
-      </c>
-      <c r="G12" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>6225</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="12"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="12"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="12"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="12"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="12"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="12"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="14">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="12"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="2">
-        <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="15">
-        <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="12"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:G1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
-      <formula>3999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G10">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
-      <formula>500</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
-      <formula>500</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C4F271-B1B8-49EF-AE8E-5ADDB846D57A}">
   <dimension ref="B4:K315"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Reagent Usage dan Stock Reagent.xlsx
+++ b/Reagent Usage dan Stock Reagent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramda\Documents\Zeta_Edit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35211DD-B11A-41BB-BA0B-30515A939761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B829621C-2FE0-4F79-B544-DA30452CAFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44BE0AC2-6033-44C2-8356-2F41A96EBF2E}"/>
   </bookViews>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="34">
   <si>
     <t>No</t>
   </si>
@@ -387,6 +387,36 @@
   </cellStyles>
   <dxfs count="15">
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -571,13 +601,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -600,6 +623,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -636,36 +666,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -686,22 +686,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1AC36863-5F67-4496-A2C7-808F86C284A1}" name="Table1" displayName="Table1" ref="B3:H21" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1AC36863-5F67-4496-A2C7-808F86C284A1}" name="Table1" displayName="Table1" ref="B3:H21" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="B3:H21" xr:uid="{1AC36863-5F67-4496-A2C7-808F86C284A1}"/>
   <tableColumns count="7">
-    <tableColumn id="2" xr3:uid="{E78837C8-954C-440F-BCB4-114AA4EBC159}" name="Kode Barang" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{BB8DB245-EB50-4D84-9B3E-D2CF46896708}" name="Nama Barang" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{36BAEBBD-D2E7-42F0-B8AF-873903FEFEA9}" name="Stok Awal " dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{3DA331B5-0C1B-4517-AC2B-660041411D0B}" name="Barang Masuk" dataDxfId="3">
+    <tableColumn id="2" xr3:uid="{E78837C8-954C-440F-BCB4-114AA4EBC159}" name="Kode Barang" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{BB8DB245-EB50-4D84-9B3E-D2CF46896708}" name="Nama Barang" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{36BAEBBD-D2E7-42F0-B8AF-873903FEFEA9}" name="Stok Awal " dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{3DA331B5-0C1B-4517-AC2B-660041411D0B}" name="Barang Masuk" dataDxfId="6">
       <calculatedColumnFormula>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4231B6CF-326F-44B2-8A60-3DCCDB55861D}" name="Barang Keluar " dataDxfId="2">
+    <tableColumn id="6" xr3:uid="{4231B6CF-326F-44B2-8A60-3DCCDB55861D}" name="Barang Keluar " dataDxfId="5">
       <calculatedColumnFormula>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{9472852C-4AF5-44FD-A6F5-E9EDEDD511AE}" name="Stock Akhir" dataDxfId="1">
+    <tableColumn id="7" xr3:uid="{9472852C-4AF5-44FD-A6F5-E9EDEDD511AE}" name="Stock Akhir" dataDxfId="4">
       <calculatedColumnFormula>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{C780F2FB-0F97-426F-AC7D-196550D5A9CF}" name="Satuan" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{C780F2FB-0F97-426F-AC7D-196550D5A9CF}" name="Satuan" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="E6" s="2">
         <f>SUMIF('Barang Masuk'!$E$5:$E$29,Table1[[#This Row],[Nama Barang]],'Barang Masuk'!$F$5:$F$29)</f>
-        <v>0</v>
+        <v>6250</v>
       </c>
       <c r="F6" s="2">
         <f>SUMIF('Barang Keluar '!$E$5:$E$315,Table1[[#This Row],[Nama Barang]],'Barang Keluar '!$F$5:$F$315)</f>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="G6" s="13">
         <f>(Table1[[#This Row],[Barang Masuk]]+Table1[[#This Row],[Stok Awal ]])-Table1[[#This Row],[Barang Keluar ]]</f>
-        <v>2025</v>
+        <v>8275</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>33</v>
@@ -1492,15 +1492,15 @@
     <mergeCell ref="B1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>3999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G10">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>500</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>500</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1598,13 +1598,19 @@
       <c r="B8" s="8">
         <v>4</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="C8" s="9">
+        <v>46280</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="E8" s="7" t="str">
         <f>IFERROR(VLOOKUP(D8,Table1[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="7"/>
+        <v>Sandios</v>
+      </c>
+      <c r="F8" s="7">
+        <v>6250</v>
+      </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="8">
